--- a/excel/excel.xlsx
+++ b/excel/excel.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\estrcutura de datos\3erParcial\excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\3erParcial\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6C80851B-7EA5-4F6C-9699-550A46B29137}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3536620-FDA9-4FDA-ADF1-D3744DB6D87E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{4D8BED8A-E98B-4E24-B6F6-F3B06260AA69}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t xml:space="preserve">Muñoz Amador Jose  Abel </t>
   </si>
@@ -48,6 +48,9 @@
   </si>
   <si>
     <t xml:space="preserve">Ortiz Reyes Moises </t>
+  </si>
+  <si>
+    <t>https://github.com/munozamadorjoseabel-cmd/Practicas3</t>
   </si>
 </sst>
 </file>
@@ -419,7 +422,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB8EB82A-B96C-49C4-A6D9-4D715CC6B992}">
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.140625" customWidth="1"/>
@@ -440,6 +443,11 @@
         <v>2</v>
       </c>
     </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
